--- a/outputs/C_scanned_inventory.xlsx
+++ b/outputs/C_scanned_inventory.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$314</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
@@ -2465,7 +2465,7 @@
         <v>0.96</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>5.193</v>
+        <v>4.479</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>5.453</v>
+        <v>6.333</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>0.96</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3.506</v>
+        <v>4.102</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3176,95 +3176,131 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>15.659</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+        <v>17.577</v>
+      </c>
+    </row>
+    <row r="4" ht="119" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Yellow cells</t>
+          <t>Text encoding</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Review required. See Validation Report for the reason and source row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>All XLSX string fields use a reversible encoding: a literal backslash is doubled; XML-forbidden code points use a backslash followed by u and four hexadecimal digits. An underscore starting an OOXML escape-like sequence uses the same Unicode encoding. Decode left to right, treating each doubled backslash as one literal backslash. The full audit JSON and saved workspace retain the original strings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Source row</t>
+          <t>Long text</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Data row within the extracted source table, excluding detected headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+          <t>Values exceeding Excel's 32767-character cell limit show an explicit preview. The Long Text sheet preserves the complete encoded value in numbered chunks. Join its chunks in order before decoding the text encoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Small numbers</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
+          <t>Numbers below Excel's normal floating-point range remain exact text. Numbers needing more than 12 decimal places use General formatting; percentages needing more than 12 display decimals remain text, avoiding a false zero.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Yellow cells</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+          <t>Review required. See Validation Report for the reason and source row.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Source row</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Source strings are stored as text. No source formulas are executed.</t>
+          <t>Data row within the extracted source table, excluding detected headers.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Cell evidence</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Source strings are stored as text. No source formulas are executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Cell evidence</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Repair proposals</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Arithmetic-derived suggestions only. Source documents may contain errors. Never applied automatically.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3379,13 +3415,13 @@
         <v>34.8</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>120</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -3426,13 +3462,13 @@
         <v>34.8</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>120</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -3473,13 +3509,13 @@
         <v>120</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>209.76</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -3520,13 +3556,13 @@
         <v>120</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>209.76</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -3567,13 +3603,13 @@
         <v>209.76</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>300</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
@@ -3614,13 +3650,13 @@
         <v>209.76</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>300</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -3661,13 +3697,13 @@
         <v>300</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>374.88</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
@@ -3708,13 +3744,13 @@
         <v>300</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>374.88</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -3755,13 +3791,13 @@
         <v>374.88</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>554.88</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
@@ -3802,13 +3838,13 @@
         <v>374.88</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>554.88</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -3849,13 +3885,13 @@
         <v>554.88</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>610.08</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
@@ -3896,13 +3932,13 @@
         <v>554.88</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>610.08</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -3943,13 +3979,13 @@
         <v>610.08</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>680.16</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
@@ -3990,13 +4026,13 @@
         <v>610.08</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>680.16</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -4037,13 +4073,13 @@
         <v>680.16</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>759.84</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
@@ -4084,13 +4120,13 @@
         <v>680.16</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>759.84</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -4131,13 +4167,13 @@
         <v>759.84</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>829.92</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -4178,13 +4214,13 @@
         <v>759.84</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>829.92</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -4225,13 +4261,13 @@
         <v>829.92</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>894.96</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
@@ -4272,13 +4308,13 @@
         <v>829.92</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>894.96</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -4319,13 +4355,13 @@
         <v>894.96</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>984.96</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
@@ -4366,13 +4402,13 @@
         <v>894.96</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>984.96</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -4413,13 +4449,13 @@
         <v>984.96</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1085.04</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
@@ -4460,13 +4496,13 @@
         <v>984.96</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1085.04</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -4507,7 +4543,7 @@
         <v>34.8</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>120</v>
@@ -4558,7 +4594,7 @@
         <v>120</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>209.76</v>
@@ -4609,7 +4645,7 @@
         <v>209.76</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>300</v>
@@ -4660,7 +4696,7 @@
         <v>300</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>374.88</v>
@@ -4711,7 +4747,7 @@
         <v>374.88</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>554.88</v>
@@ -4762,7 +4798,7 @@
         <v>554.88</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>610.08</v>
@@ -4813,7 +4849,7 @@
         <v>610.08</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>680.16</v>
@@ -4864,7 +4900,7 @@
         <v>680.16</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>759.84</v>
@@ -4915,7 +4951,7 @@
         <v>759.84</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>829.92</v>
@@ -4966,7 +5002,7 @@
         <v>829.92</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>894.96</v>
@@ -5017,7 +5053,7 @@
         <v>894.96</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>984.96</v>
@@ -5068,7 +5104,7 @@
         <v>984.96</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1085.04</v>
@@ -11902,7 +11938,7 @@
         <v>34.8</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>120</v>
@@ -11953,7 +11989,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>209.76</v>
@@ -12004,7 +12040,7 @@
         <v>209.76</v>
       </c>
       <c r="F173" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>300</v>
@@ -12055,7 +12091,7 @@
         <v>300</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>374.88</v>
@@ -12106,7 +12142,7 @@
         <v>374.88</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>554.88</v>
@@ -12157,7 +12193,7 @@
         <v>554.88</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>610.08</v>
@@ -12208,7 +12244,7 @@
         <v>610.08</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>680.16</v>
@@ -12259,7 +12295,7 @@
         <v>680.16</v>
       </c>
       <c r="F178" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>759.84</v>
@@ -12310,7 +12346,7 @@
         <v>759.84</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>829.92</v>
@@ -12361,7 +12397,7 @@
         <v>829.92</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>894.96</v>
@@ -12412,7 +12448,7 @@
         <v>894.96</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G181" s="7" t="n">
         <v>984.96</v>
@@ -12463,7 +12499,7 @@
         <v>984.96</v>
       </c>
       <c r="F182" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>1085.04</v>
@@ -19278,7 +19314,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>e49b185ea741e9454d861b921c8a217a8e0c1cadd09687371b0ce506c0d8a103</t>
+          <t>0cb86c7728a86dde04abfb7fd430acc1fd7d78d2c8519cf3712c6fc6b868dadf</t>
         </is>
       </c>
     </row>

--- a/outputs/C_scanned_inventory.xlsx
+++ b/outputs/C_scanned_inventory.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$314</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2082,6 +2084,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -2465,7 +2540,7 @@
         <v>0.96</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>4.479</v>
+        <v>10.026</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2507,7 +2582,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>6.333</v>
+        <v>7.397</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2549,7 +2624,7 @@
         <v>0.96</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>4.102</v>
+        <v>5.303</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2580,6 +2655,133 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3132,7 +3334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3176,7 +3378,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>17.577</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -3305,7 +3507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19269,7 +19471,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19314,7 +19516,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>0cb86c7728a86dde04abfb7fd430acc1fd7d78d2c8519cf3712c6fc6b868dadf</t>
+          <t>26bde550dcad7c7fea0e451a150ff4d57090dc6dae0c133e5774ffd5435ce910</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19513,77 +19715,4 @@
   <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>